--- a/Assets/@Project/Scripts/SpecData/Xlsx/Spec.xlsx
+++ b/Assets/@Project/Scripts/SpecData/Xlsx/Spec.xlsx
@@ -5,16 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\RogueLikeTemplate\Assets\@Project\Scripts\SpecData\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ChainBall\Assets\@Project\Scripts\SpecData\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDCFCB9-792D-4DED-8898-EB59927D71EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D965D8-C220-4FC5-A3C0-8C945D797747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#enum" sheetId="1" r:id="rId1"/>
     <sheet name="SpecLocalize" sheetId="2" r:id="rId2"/>
+    <sheet name="SpecHitInstance" sheetId="3" r:id="rId3"/>
+    <sheet name="SpecModifier" sheetId="4" r:id="rId4"/>
+    <sheet name="SpecTrigger" sheetId="5" r:id="rId5"/>
+    <sheet name="SpecWeapon" sheetId="6" r:id="rId6"/>
+    <sheet name="SpecWave" sheetId="7" r:id="rId7"/>
+    <sheet name="SpecRelic" sheetId="8" r:id="rId8"/>
+    <sheet name="SpecEffect" sheetId="9" r:id="rId9"/>
+    <sheet name="SpecCharacter" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="234">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,13 +60,697 @@
   <si>
     <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eHitInstanceKind</t>
+  </si>
+  <si>
+    <t>value:eHitInstanceKind</t>
+  </si>
+  <si>
+    <t>eProjectileMotion</t>
+  </si>
+  <si>
+    <t>value:eProjectileMotion</t>
+  </si>
+  <si>
+    <t>eRarity</t>
+  </si>
+  <si>
+    <t>value:eRarity</t>
+  </si>
+  <si>
+    <t>eElement</t>
+  </si>
+  <si>
+    <t>value:eElement</t>
+  </si>
+  <si>
+    <t>eModifierBehavior</t>
+  </si>
+  <si>
+    <t>value:eModifierBehavior</t>
+  </si>
+  <si>
+    <t>eTriggerEvent</t>
+  </si>
+  <si>
+    <t>value:eTriggerEvent</t>
+  </si>
+  <si>
+    <t>eEffectKind</t>
+  </si>
+  <si>
+    <t>value:eEffectKind</t>
+  </si>
+  <si>
+    <t>eRelicCategory</t>
+  </si>
+  <si>
+    <t>value:eRelicCategory</t>
+  </si>
+  <si>
+    <t>eRelicHook</t>
+  </si>
+  <si>
+    <t>value:eRelicHook</t>
+  </si>
+  <si>
+    <t>eRelicCondition</t>
+  </si>
+  <si>
+    <t>value:eRelicCondition</t>
+  </si>
+  <si>
+    <t>eSlotKind</t>
+  </si>
+  <si>
+    <t>value:eSlotKind</t>
+  </si>
+  <si>
+    <t>eUnlockCondition</t>
+  </si>
+  <si>
+    <t>value:eUnlockCondition</t>
+  </si>
+  <si>
+    <t>eBossPattern</t>
+  </si>
+  <si>
+    <t>value:eBossPattern</t>
+  </si>
+  <si>
+    <t>MOVING</t>
+  </si>
+  <si>
+    <t>INSTANT</t>
+  </si>
+  <si>
+    <t>AURA</t>
+  </si>
+  <si>
+    <t>STRAIGHT</t>
+  </si>
+  <si>
+    <t>REFLECT</t>
+  </si>
+  <si>
+    <t>HOMING</t>
+  </si>
+  <si>
+    <t>CURVE</t>
+  </si>
+  <si>
+    <t>STATIC</t>
+  </si>
+  <si>
+    <t>FALLING</t>
+  </si>
+  <si>
+    <t>COMMON</t>
+  </si>
+  <si>
+    <t>UNCOMMON</t>
+  </si>
+  <si>
+    <t>RARE</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>FIRE</t>
+  </si>
+  <si>
+    <t>ICE</t>
+  </si>
+  <si>
+    <t>SHOCK</t>
+  </si>
+  <si>
+    <t>SPLIT</t>
+  </si>
+  <si>
+    <t>PIERCE_ON_HIT</t>
+  </si>
+  <si>
+    <t>CHAIN</t>
+  </si>
+  <si>
+    <t>CLONE_AT_FIRE</t>
+  </si>
+  <si>
+    <t>FREEZE_ROW</t>
+  </si>
+  <si>
+    <t>BRICK_HIT</t>
+  </si>
+  <si>
+    <t>BRICK_KILL</t>
+  </si>
+  <si>
+    <t>WALL_BOUNCE</t>
+  </si>
+  <si>
+    <t>PROJECTILE_DESPAWN</t>
+  </si>
+  <si>
+    <t>NTH_BRICK_HIT</t>
+  </si>
+  <si>
+    <t>ELEMENT_MATCH</t>
+  </si>
+  <si>
+    <t>LINE_CLEAR</t>
+  </si>
+  <si>
+    <t>DANGER_PROXIMITY</t>
+  </si>
+  <si>
+    <t>CONSECUTIVE_HIT</t>
+  </si>
+  <si>
+    <t>FULL_BOUNCE</t>
+  </si>
+  <si>
+    <t>DAMAGE_DIRECT</t>
+  </si>
+  <si>
+    <t>AOE_DAMAGE</t>
+  </si>
+  <si>
+    <t>LINE_DAMAGE</t>
+  </si>
+  <si>
+    <t>CHAIN_DAMAGE</t>
+  </si>
+  <si>
+    <t>STATUS_BURN</t>
+  </si>
+  <si>
+    <t>STATUS_FREEZE</t>
+  </si>
+  <si>
+    <t>HEAL</t>
+  </si>
+  <si>
+    <t>GOLD_GAIN</t>
+  </si>
+  <si>
+    <t>SPAWN_HIT_INSTANCE</t>
+  </si>
+  <si>
+    <t>EXTRA_CAST</t>
+  </si>
+  <si>
+    <t>OVERKILL_TRANSFER</t>
+  </si>
+  <si>
+    <t>HALF_HP_REMOVE</t>
+  </si>
+  <si>
+    <t>GRAVITY_PULL</t>
+  </si>
+  <si>
+    <t>BURN_DETONATE</t>
+  </si>
+  <si>
+    <t>EMPOWER_NEXT</t>
+  </si>
+  <si>
+    <t>DAMAGE</t>
+  </si>
+  <si>
+    <t>BOUNCE</t>
+  </si>
+  <si>
+    <t>MULTI_SHOT</t>
+  </si>
+  <si>
+    <t>SURVIVAL</t>
+  </si>
+  <si>
+    <t>ECONOMY</t>
+  </si>
+  <si>
+    <t>UTILITY</t>
+  </si>
+  <si>
+    <t>SYNERGY</t>
+  </si>
+  <si>
+    <t>PASSIVE_GLOBAL</t>
+  </si>
+  <si>
+    <t>ON_HIT</t>
+  </si>
+  <si>
+    <t>ON_KILL</t>
+  </si>
+  <si>
+    <t>ON_BOUNCE</t>
+  </si>
+  <si>
+    <t>ON_BOUNCE_EXHAUSTED</t>
+  </si>
+  <si>
+    <t>ON_PROJECTILE_DESPAWN</t>
+  </si>
+  <si>
+    <t>ON_TURN_END</t>
+  </si>
+  <si>
+    <t>ON_BATTLE_END</t>
+  </si>
+  <si>
+    <t>ON_BATTLE_START</t>
+  </si>
+  <si>
+    <t>ON_DAMAGE_TAKEN</t>
+  </si>
+  <si>
+    <t>ON_FATAL</t>
+  </si>
+  <si>
+    <t>ON_BRICK_DESTROY</t>
+  </si>
+  <si>
+    <t>ON_SHOP_OPEN</t>
+  </si>
+  <si>
+    <t>BRICK_HP_EQ</t>
+  </si>
+  <si>
+    <t>BRICK_HP_LT_PCT</t>
+  </si>
+  <si>
+    <t>WITHIN_DANGER_ROW</t>
+  </si>
+  <si>
+    <t>WALL_BOUNCE_LR</t>
+  </si>
+  <si>
+    <t>SAME_BRICK_HITS_GE</t>
+  </si>
+  <si>
+    <t>PLAYER_HP_LT_PCT</t>
+  </si>
+  <si>
+    <t>BRICKS_KILLED_THIS_CAST_GE</t>
+  </si>
+  <si>
+    <t>NO_DAMAGE_TAKEN_PREV_BATTLE</t>
+  </si>
+  <si>
+    <t>IN_ELITE_BATTLE</t>
+  </si>
+  <si>
+    <t>ANY</t>
+  </si>
+  <si>
+    <t>TRIGGER</t>
+  </si>
+  <si>
+    <t>PROJECTILE</t>
+  </si>
+  <si>
+    <t>MODIFIER</t>
+  </si>
+  <si>
+    <t>EFFECT</t>
+  </si>
+  <si>
+    <t>ALWAYS</t>
+  </si>
+  <si>
+    <t>FIRST_CLEAR</t>
+  </si>
+  <si>
+    <t>ELITE_KILLS_GE</t>
+  </si>
+  <si>
+    <t>BOSS_KILLS_GE</t>
+  </si>
+  <si>
+    <t>RUN_COUNT_GE</t>
+  </si>
+  <si>
+    <t>BOSS_01_OPENING</t>
+  </si>
+  <si>
+    <t>BOSS_01_TELEGRAPH</t>
+  </si>
+  <si>
+    <t>BOSS_01_RAGE</t>
+  </si>
+  <si>
+    <t>w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecHitInstance</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>nameKey</t>
+  </si>
+  <si>
+    <t>descKey</t>
+  </si>
+  <si>
+    <t>rarity</t>
+  </si>
+  <si>
+    <t>motion</t>
+  </si>
+  <si>
+    <t>baseDamage</t>
+  </si>
+  <si>
+    <t>basePercent</t>
+  </si>
+  <si>
+    <t>effects</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>moveSpeed</t>
+  </si>
+  <si>
+    <t>lifeTime</t>
+  </si>
+  <si>
+    <t>hitCount</t>
+  </si>
+  <si>
+    <t>bounceCount</t>
+  </si>
+  <si>
+    <t>pierceCount</t>
+  </si>
+  <si>
+    <t>passThrough</t>
+  </si>
+  <si>
+    <t>homing</t>
+  </si>
+  <si>
+    <t>randomAngle</t>
+  </si>
+  <si>
+    <t>hitWidth</t>
+  </si>
+  <si>
+    <t>multiShot</t>
+  </si>
+  <si>
+    <t>spreadAngle</t>
+  </si>
+  <si>
+    <t>staticAfterFire</t>
+  </si>
+  <si>
+    <t>tickInterval</t>
+  </si>
+  <si>
+    <t>vfxKey</t>
+  </si>
+  <si>
+    <t>sfxKey</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>enum:eHitInstanceKind</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>enum:eRarity</t>
+  </si>
+  <si>
+    <t>enum:eProjectileMotion</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>SpecEffect</t>
+  </si>
+  <si>
+    <t>damageDelta</t>
+  </si>
+  <si>
+    <t>damageMul</t>
+  </si>
+  <si>
+    <t>damageMin</t>
+  </si>
+  <si>
+    <t>bounceDelta</t>
+  </si>
+  <si>
+    <t>pierceDelta</t>
+  </si>
+  <si>
+    <t>hitWidthMul</t>
+  </si>
+  <si>
+    <t>speedMul</t>
+  </si>
+  <si>
+    <t>behavior</t>
+  </si>
+  <si>
+    <t>behaviorParam1</t>
+  </si>
+  <si>
+    <t>behaviorParam2</t>
+  </si>
+  <si>
+    <t>behaviorParamF</t>
+  </si>
+  <si>
+    <t>element</t>
+  </si>
+  <si>
+    <t>cooldownTurn</t>
+  </si>
+  <si>
+    <t>enum:eModifierBehavior</t>
+  </si>
+  <si>
+    <t>enum:eElement</t>
+  </si>
+  <si>
+    <t>SpecModifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecTrigger</t>
+  </si>
+  <si>
+    <t>nthCount</t>
+  </si>
+  <si>
+    <t>elementMatch</t>
+  </si>
+  <si>
+    <t>proximityRow</t>
+  </si>
+  <si>
+    <t>maxFiresPerCast</t>
+  </si>
+  <si>
+    <t>enum:eTriggerEvent</t>
+  </si>
+  <si>
+    <t>eventType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecWeapon</t>
+  </si>
+  <si>
+    <t>slotCount</t>
+  </si>
+  <si>
+    <t>castsPerTurn</t>
+  </si>
+  <si>
+    <t>cooldownTurns</t>
+  </si>
+  <si>
+    <t>slotShape</t>
+  </si>
+  <si>
+    <t>multiAngle</t>
+  </si>
+  <si>
+    <t>iconKey</t>
+  </si>
+  <si>
+    <t>enum[]:eSlotKind</t>
+  </si>
+  <si>
+    <t>SpecWave</t>
+  </si>
+  <si>
+    <t>waveId</t>
+  </si>
+  <si>
+    <t>lineIndex</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>bossLine</t>
+  </si>
+  <si>
+    <t>bossPattern</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>enum:eBossPattern</t>
+  </si>
+  <si>
+    <t>SpecRelic</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>hook</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>condParam1</t>
+  </si>
+  <si>
+    <t>condParam2</t>
+  </si>
+  <si>
+    <t>extraCast</t>
+  </si>
+  <si>
+    <t>extraCastDamageDelta</t>
+  </si>
+  <si>
+    <t>chance</t>
+  </si>
+  <si>
+    <t>triggerEffectId</t>
+  </si>
+  <si>
+    <t>usesPerRun</t>
+  </si>
+  <si>
+    <t>synergyAxis</t>
+  </si>
+  <si>
+    <t>enum:eRelicCategory</t>
+  </si>
+  <si>
+    <t>enum:eRelicHook</t>
+  </si>
+  <si>
+    <t>enum:eRelicCondition</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>targetCount</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>tickDamage</t>
+  </si>
+  <si>
+    <t>healAmount</t>
+  </si>
+  <si>
+    <t>goldAmount</t>
+  </si>
+  <si>
+    <t>spawnHitInstance</t>
+  </si>
+  <si>
+    <t>spawnCount</t>
+  </si>
+  <si>
+    <t>enum:eEffectKind</t>
+  </si>
+  <si>
+    <t>SpecCharacter</t>
+  </si>
+  <si>
+    <t>passiveId</t>
+  </si>
+  <si>
+    <t>commonPool</t>
+  </si>
+  <si>
+    <t>exclusivePool0</t>
+  </si>
+  <si>
+    <t>exclusivePool1</t>
+  </si>
+  <si>
+    <t>exclusivePool2</t>
+  </si>
+  <si>
+    <t>unlockPhase1</t>
+  </si>
+  <si>
+    <t>unlockPhase1Param</t>
+  </si>
+  <si>
+    <t>unlockPhase2</t>
+  </si>
+  <si>
+    <t>unlockPhase2Param</t>
+  </si>
+  <si>
+    <t>startWeaponId</t>
+  </si>
+  <si>
+    <t>startHp</t>
+  </si>
+  <si>
+    <t>enum:eUnlockCondition</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,8 +772,46 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -94,8 +824,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -122,9 +876,7 @@
       <left style="medium">
         <color rgb="FFCCCCCC"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
+      <right/>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
       </top>
@@ -133,17 +885,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF333333"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,29 +1251,872 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{7C8CFA81-8D36-4545-9B2B-A3A8DA8DA1D1}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="ko-KR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;3123f78d-8efb-4f0d-9ce5-7972e7a2d8f3&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.125" customWidth="1"/>
+    <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="34.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R3" s="4">
+        <v>1</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="T3" s="4">
+        <v>1</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4" t="s">
+        <v>87</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4" t="s">
+        <v>99</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>109</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>81</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="S5" t="s">
+        <v>88</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5" t="s">
+        <v>100</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5" t="s">
+        <v>110</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z5">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>82</v>
+      </c>
+      <c r="R6">
+        <v>4</v>
+      </c>
+      <c r="S6" t="s">
+        <v>89</v>
+      </c>
+      <c r="T6">
+        <v>4</v>
+      </c>
+      <c r="U6" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6" t="s">
+        <v>111</v>
+      </c>
+      <c r="X6">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T7">
+        <v>5</v>
+      </c>
+      <c r="U7" t="s">
+        <v>102</v>
+      </c>
+      <c r="V7">
+        <v>4</v>
+      </c>
+      <c r="W7" t="s">
+        <v>112</v>
+      </c>
+      <c r="X7">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8">
+        <v>6</v>
+      </c>
+      <c r="O8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8">
+        <v>6</v>
+      </c>
+      <c r="S8" t="s">
+        <v>91</v>
+      </c>
+      <c r="T8">
+        <v>6</v>
+      </c>
+      <c r="U8" t="s">
+        <v>103</v>
+      </c>
+      <c r="V8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9">
+        <v>7</v>
+      </c>
+      <c r="O9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R9">
+        <v>7</v>
+      </c>
+      <c r="S9" t="s">
+        <v>92</v>
+      </c>
+      <c r="T9">
+        <v>7</v>
+      </c>
+      <c r="U9" t="s">
+        <v>104</v>
+      </c>
+      <c r="V9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10">
+        <v>8</v>
+      </c>
+      <c r="O10" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10">
+        <v>8</v>
+      </c>
+      <c r="S10" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10">
+        <v>8</v>
+      </c>
+      <c r="U10" t="s">
+        <v>105</v>
+      </c>
+      <c r="V10">
+        <v>7</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="M11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11">
+        <v>9</v>
+      </c>
+      <c r="O11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11">
+        <v>9</v>
+      </c>
+      <c r="S11" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11">
+        <v>9</v>
+      </c>
+      <c r="U11" t="s">
+        <v>106</v>
+      </c>
+      <c r="V11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12">
+        <v>10</v>
+      </c>
+      <c r="O12" t="s">
+        <v>73</v>
+      </c>
+      <c r="P12">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>95</v>
+      </c>
+      <c r="T12">
+        <v>10</v>
+      </c>
+      <c r="U12" t="s">
+        <v>107</v>
+      </c>
+      <c r="V12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13">
+        <v>11</v>
+      </c>
+      <c r="S13" t="s">
+        <v>96</v>
+      </c>
+      <c r="T13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="O14" t="s">
+        <v>75</v>
+      </c>
+      <c r="P14">
+        <v>12</v>
+      </c>
+      <c r="S14" t="s">
+        <v>97</v>
+      </c>
+      <c r="T14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="O15" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15">
+        <v>13</v>
+      </c>
+      <c r="S15" t="s">
+        <v>98</v>
+      </c>
+      <c r="T15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="O16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="15:16" x14ac:dyDescent="0.3">
+      <c r="O17" t="s">
+        <v>78</v>
+      </c>
+      <c r="P17">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC9EAAD-F259-4BD0-B955-52A45D132A62}">
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -485,4 +2156,968 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CCBA5D1-1E05-49FB-A76E-47D26051D626}">
+  <dimension ref="A1:Y3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251C2917-6467-48D3-B16C-6962356F837A}">
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF385B4-42C3-4ED8-8BFB-516EA65BCD26}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E139B588-AE33-4B67-A179-5FC380177F03}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C985EE0E-FA2D-4C6F-8991-5D591A6B1F6C}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F02134B-5EC5-441E-AE52-E203BD5B3BAB}">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5EAC8A-D239-4081-BA7D-9E63E77C916D}">
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:18" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/@Project/Scripts/SpecData/Xlsx/Spec.xlsx
+++ b/Assets/@Project/Scripts/SpecData/Xlsx/Spec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ChainBall\Assets\@Project\Scripts\SpecData\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D965D8-C220-4FC5-A3C0-8C945D797747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14709B0A-9065-4348-8174-F232CAFE43E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#enum" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="SpecRelic" sheetId="8" r:id="rId8"/>
     <sheet name="SpecEffect" sheetId="9" r:id="rId9"/>
     <sheet name="SpecCharacter" sheetId="10" r:id="rId10"/>
+    <sheet name="SpecEnemy" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="261">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -744,13 +745,97 @@
   </si>
   <si>
     <t>enum:eUnlockCondition</t>
+  </si>
+  <si>
+    <t>controllerId</t>
+  </si>
+  <si>
+    <t>controllerId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viewId</t>
+  </si>
+  <si>
+    <t>viewId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brick_NORMAL</t>
+  </si>
+  <si>
+    <t>brick_shield_FIRE</t>
+  </si>
+  <si>
+    <t>brick_shield_ICE</t>
+  </si>
+  <si>
+    <t>brick_shield_SHOCK</t>
+  </si>
+  <si>
+    <t>brick_EXPLOSIVE</t>
+  </si>
+  <si>
+    <t>brick_SPAWNER</t>
+  </si>
+  <si>
+    <t>brick_REFLECTOR</t>
+  </si>
+  <si>
+    <t>enemy.brick_normal.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_normal.desc</t>
+  </si>
+  <si>
+    <t>enemy.brick_shield_fire.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_shield_fire.desc</t>
+  </si>
+  <si>
+    <t>enemy.brick_shield_ice.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_shield_ice.desc</t>
+  </si>
+  <si>
+    <t>enemy.brick_shield_shock.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_shield_shock.desc</t>
+  </si>
+  <si>
+    <t>enemy.brick_explosive.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_explosive.desc</t>
+  </si>
+  <si>
+    <t>enemy.brick_spawner.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_spawner.desc</t>
+  </si>
+  <si>
+    <t>enemy.brick_reflector.name</t>
+  </si>
+  <si>
+    <t>enemy.brick_reflector.desc</t>
+  </si>
+  <si>
+    <t>SpecEnemy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,6 +893,49 @@
       <color rgb="FF444444"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -944,7 +1072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -973,6 +1101,15 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1253,7 +1390,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="0" width="405" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1988,14 +2125,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC9EAAD-F259-4BD0-B955-52A45D132A62}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="15.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.375" bestFit="1" customWidth="1"/>
@@ -2006,7 +2143,7 @@
     <col min="15" max="15" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>221</v>
       </c>
@@ -2024,8 +2161,10 @@
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>123</v>
       </c>
@@ -2036,43 +2175,49 @@
         <v>126</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="P2" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="Q2" s="10" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>150</v>
       </c>
@@ -2083,13 +2228,13 @@
         <v>150</v>
       </c>
       <c r="D3" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>194</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>194</v>
@@ -2098,10 +2243,10 @@
         <v>194</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="K3" s="11" t="s">
         <v>233</v>
@@ -2110,7 +2255,7 @@
         <v>148</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>148</v>
@@ -2118,6 +2263,236 @@
       <c r="O3" s="11" t="s">
         <v>150</v>
       </c>
+      <c r="P3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7202CDBC-2B8E-46C7-97D9-78B8DF751455}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="16">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
+        <v>1</v>
+      </c>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16">
+        <v>2</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16">
+        <v>2</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" s="16">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16">
+        <v>2</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1</v>
+      </c>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" s="16">
+        <v>1</v>
+      </c>
+      <c r="E8" s="16">
+        <v>3</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="D9" s="16">
+        <v>1</v>
+      </c>
+      <c r="E9" s="16">
+        <v>4</v>
+      </c>
+      <c r="F9" s="16">
+        <v>2</v>
+      </c>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="16">
+        <v>1</v>
+      </c>
+      <c r="E10" s="16">
+        <v>5</v>
+      </c>
+      <c r="F10" s="16">
+        <v>99</v>
+      </c>
+      <c r="G10" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
